--- a/ig/ch-elm/StructureDefinition-ch-elm-diagnosticreport.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-diagnosticreport.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -371,7 +371,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -876,7 +876,7 @@
     <t>Codes for diagnostic service sections.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
@@ -1001,7 +1001,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1139,7 +1139,7 @@
 Reported by</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1)
 </t>
   </si>
   <si>
@@ -1206,7 +1206,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ImagingStudy)
+    <t xml:space="preserve">Reference(ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -1289,7 +1289,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media)
+    <t xml:space="preserve">Reference(Media|4.0.1)
 </t>
   </si>
   <si>
@@ -1336,7 +1336,7 @@
     <t>Diagnosis codes provided as adjuncts to the report.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=SPRT].source[classCode=OBS, moodCode=EVN, code=LOINC:54531-9].value (type=CD)</t>
@@ -1693,7 +1693,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.6484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.3515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/ig/ch-elm/StructureDefinition-ch-elm-diagnosticreport.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-diagnosticreport.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-diagnosticreport.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-diagnosticreport.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-diagnosticreport.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-diagnosticreport.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
